--- a/Documentacion Sprint (01 - 11)/Sprint 4 documentacion/Sprint_04_Backlog_ICARO.xlsx
+++ b/Documentacion Sprint (01 - 11)/Sprint 4 documentacion/Sprint_04_Backlog_ICARO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 4 documentacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentacion Sprint (01 - 11)\Sprint 4 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B4D9D0-DA3C-4DE0-821F-66F756BA219B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9363C27E-8541-4BEB-AD22-F711B69A1006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog Sprint 04" sheetId="4" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="214">
   <si>
     <t>ICARO CONSTRUCTORES BMGM S.A.S.</t>
   </si>
@@ -662,6 +662,9 @@
   </si>
   <si>
     <t>RESUMEN DE CASOS DE PRUEBA — SPRINT 04 (CP-051 a CP-068)</t>
+  </si>
+  <si>
+    <t>Los estados presentados en este documento corresponden al estado del Product/Sprint Backlog al cierre del Sprint respectivo. Debido a la naturaleza iterativa e incremental del proyecto, los elementos identificados como pendientes, diferidos o parcialmente implementados pudieron ser desarrollados y completados en sprints posteriores. Para conocer el estado definitivo de cada historia de usuario o historia técnica, debe consultarse el Product Backlog Consolidado al cierre del proyecto.</t>
   </si>
 </sst>
 </file>
@@ -765,7 +768,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -814,8 +817,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -938,12 +946,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1011,6 +1035,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1052,9 +1079,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="40% - Énfasis3" xfId="1" builtinId="39"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Notas" xfId="2" builtinId="10"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -1536,7 +1564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{023A4DB3-4E78-4D63-B506-FBDBD8DF719F}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34.5703125" customWidth="1"/>
@@ -1549,124 +1577,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="27"/>
       <c r="G3" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="H3" s="27">
+      <c r="H3" s="28">
         <v>4</v>
       </c>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="30"/>
     </row>
     <row r="4" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="36">
         <v>46116</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="38"/>
       <c r="G4" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="35">
+      <c r="H4" s="36">
         <v>46150</v>
       </c>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="38"/>
     </row>
     <row r="5" spans="1:12" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="27"/>
       <c r="G5" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="27"/>
     </row>
     <row r="6" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <v>22</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="30"/>
       <c r="G6" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="27"/>
     </row>
     <row r="7" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
@@ -1935,13 +1963,13 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="15">
         <v>22</v>
       </c>
@@ -1954,14 +1982,66 @@
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H4:L4"/>
+    <mergeCell ref="A16:E22"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="H5:L5"/>
     <mergeCell ref="B6:F6"/>
@@ -1983,12 +2063,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2177,11 +2257,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -2378,14 +2458,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
